--- a/data/merged/2026-09-09/MERGED_FR_Wet-Dry-Floor-Washer_2026-09-09.xlsx
+++ b/data/merged/2026-09-09/MERGED_FR_Wet-Dry-Floor-Washer_2026-09-09.xlsx
@@ -805,13 +805,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>1</xdr:row>
+      <xdr:row>2</xdr:row>
       <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>1</xdr:row>
+      <xdr:row>2</xdr:row>
       <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -829,50 +829,6 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip r:embed="rId1" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Product 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId2" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1214,7 +1170,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR4"/>
+  <dimension ref="A1:BR3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -1629,57 +1585,45 @@
       <c r="B2" s="13"/>
       <c r="C2" s="14" t="inlineStr">
         <is>
-          <t>B0H69GTK93</t>
+          <t>B0G7GJZ7WQ</t>
         </is>
       </c>
       <c r="D2" s="14"/>
-      <c r="E2" s="14" t="inlineStr">
-        <is>
-          <t>Marque: Generic | Caractéristique spéciale: Sans fil | Type de filtre: Filtre HEPA | Recommandation de surface: Maison | Source d'alimentation: Alimenté par batterie | Composants inclus: Accessoires pour sols durs, moquettes et tissus | Sans fil ?: Oui | Capacité: 1,5 litres | Utilisations recommandées pour le produit: Sols durs, moquettes, tissus, escaliers, voitures | Facteur de forme: Bâton</t>
-        </is>
-      </c>
+      <c r="E2" s="14"/>
       <c r="F2" s="14" t="inlineStr">
         <is>
-          <t>Generic</t>
+          <t>JONR</t>
         </is>
       </c>
       <c r="G2" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Generic</t>
+          <t>https://www.amazon.fr/stores/JONR/page/2E11CD6D-6ABC-4227-8074-804128923C6D?lp_asin=B0H3NZP2VD&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H2" s="14" t="inlineStr">
         <is>
-          <t>Aspirateur sans Fil 50000Pa 600W 60Min Autonomie Grand Bac À Poussière Filtration 8 Étages pour Maison Poils Animaux</t>
-        </is>
-      </c>
-      <c r="I2" s="14" t="inlineStr">
-        <is>
-          <t>Puissance D’aspiration 50000Pa - Moteur Haute Performance Produisant 50000Pa D’aspiration Élimine La Poussière Profonde Les Acariens Et Les Poils D’animaux
-Moteur 600W Haute Efficacité - Moteur Numérique De 600W Offre Une Efficacité Énergétique Constante Sur Tous Les Types De Sols
-60 Minutes D’autonomie - Batterie Haute Capacité Assure Jusqu’à 60 Minutes De Nettoyage En Continu Idéal Pour Les Grandes Surfaces
-Filtration À 8 Étages - Système De Filtration Avancé Avec Filtre Hepa Capture 99.99% Des Particules Fines Et Allergènes
-Grand Bac À Poussière - Capacité De 1.5 Litres Réduit Les Vidages Fréquents Pratique Pour Les Grands Ménages</t>
-        </is>
-      </c>
+          <t>JONR Aspirateur Eau et poussière 20 000 Pa H2, Design innovant sans Odeur, réservoir d'eau Extra Large de 1500 ML avec Plat à</t>
+        </is>
+      </c>
+      <c r="I2" s="14"/>
       <c r="J2" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0H69GTK93?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0G7GJZ7WQ?psc=1</t>
         </is>
       </c>
       <c r="K2" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/710l9PXoMvL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61ruaomVmXL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L2" s="14" t="inlineStr">
         <is>
-          <t>B0H69GTK93</t>
+          <t>B0G7GJZ7WQ</t>
         </is>
       </c>
       <c r="M2" s="14" t="inlineStr">
         <is>
-          <t>Cuisine et Maison:Aspirateurs, entretien des sols et nettoyeurs de vitres:Aspirateurs:Aspirateurs eau et poussière à usage domestique</t>
+          <t>Cuisine et Maison:Aspirateurs, entretien des sols et nettoyeurs de vitres:Aspirateurs:Aspirateurs balais et balais électriques</t>
         </is>
       </c>
       <c r="N2" s="14" t="inlineStr">
@@ -1688,94 +1632,92 @@
         </is>
       </c>
       <c r="O2" s="15">
-        <v>532265</v>
+        <v>1048114</v>
       </c>
       <c r="P2" s="2"/>
       <c r="Q2" s="16">
         <v>0</v>
       </c>
-      <c r="R2" s="17" t="inlineStr">
-        <is>
-          <t>Aspirateurs eau et poussière à usage domestique</t>
-        </is>
-      </c>
-      <c r="S2" s="18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T2" s="15">
-        <v>6</v>
-      </c>
+      <c r="R2" s="17"/>
+      <c r="S2" s="18"/>
+      <c r="T2" s="15"/>
       <c r="U2" s="16"/>
-      <c r="V2" s="15">
-        <v>240</v>
-      </c>
+      <c r="V2" s="15"/>
       <c r="W2" s="15"/>
       <c r="X2" s="15"/>
       <c r="Y2" s="19">
         <v>1</v>
       </c>
       <c r="Z2" s="20">
-        <v>39.99</v>
+        <v>199.99</v>
       </c>
       <c r="AA2" s="4"/>
       <c r="AB2" s="1"/>
       <c r="AC2" s="2"/>
       <c r="AD2" s="19">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="AE2" s="15">
         <v>0</v>
       </c>
       <c r="AF2" s="21">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AG2" s="22">
         <v>0</v>
       </c>
       <c r="AH2" s="20">
-        <v>8.44</v>
+        <v>10.27</v>
       </c>
       <c r="AI2" s="16">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="AJ2"/>
       <c r="AK2" s="13" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="AL2" s="19">
-        <v>59</v>
+        <v>173</v>
       </c>
       <c r="AM2" s="13" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AN2" s="13"/>
       <c r="AO2" s="13"/>
       <c r="AP2" s="4"/>
-      <c r="AQ2" s="19"/>
+      <c r="AQ2" s="19">
+        <v>9</v>
+      </c>
       <c r="AR2" s="19">
         <v>1</v>
       </c>
       <c r="AS2" s="14" t="inlineStr">
         <is>
-          <t>CHENMW Department Store</t>
+          <t>JONR Official</t>
         </is>
       </c>
       <c r="AT2" s="13" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU2" s="13"/>
-      <c r="AV2" s="14"/>
+          <t>FBA</t>
+        </is>
+      </c>
+      <c r="AU2" s="13" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="AV2" s="14" t="inlineStr">
+        <is>
+          <t>苏州市 江苏 215028 CN</t>
+        </is>
+      </c>
       <c r="AW2" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AQBFEG6BI2O00</t>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1R6H4HF5LIC6Y</t>
         </is>
       </c>
       <c r="AX2" s="13"/>
@@ -1783,8 +1725,16 @@
       <c r="AZ2" s="13"/>
       <c r="BA2" s="13"/>
       <c r="BB2" s="13"/>
-      <c r="BC2" s="13"/>
-      <c r="BD2" s="13"/>
+      <c r="BC2" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BD2" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE2" s="13"/>
       <c r="BF2" s="13"/>
       <c r="BG2" s="13"/>
@@ -1792,43 +1742,47 @@
       <c r="BI2"/>
       <c r="BJ2" s="23" t="inlineStr">
         <is>
-          <t>4,46 Kilograms</t>
+          <t>3.5 kg</t>
         </is>
       </c>
       <c r="BK2" s="23" t="inlineStr">
         <is>
-          <t>4.46 kg</t>
+          <t>3.50 kg</t>
         </is>
       </c>
       <c r="BL2" s="23" t="inlineStr">
         <is>
-          <t>12L x 7l x 18H centimètres</t>
-        </is>
-      </c>
-      <c r="BM2" s="23"/>
+          <t>26.9 x 21 x 109.9 cm</t>
+        </is>
+      </c>
+      <c r="BM2" s="23" t="inlineStr">
+        <is>
+          <t>26.90 x 21.00 x 109.90 cm</t>
+        </is>
+      </c>
       <c r="BN2" s="23" t="inlineStr">
         <is>
-          <t>4.46 kg</t>
+          <t>6.78 kg</t>
         </is>
       </c>
       <c r="BO2" s="23" t="inlineStr">
         <is>
-          <t>4.46 kg</t>
+          <t>6.78 kg</t>
         </is>
       </c>
       <c r="BP2" s="23" t="inlineStr">
         <is>
-          <t>44.5 x 33.6 x 19.5 cm</t>
+          <t>61 x 33.8 x 32.3 cm</t>
         </is>
       </c>
       <c r="BQ2" s="23" t="inlineStr">
         <is>
-          <t>44.50 x 33.60 x 19.50 cm</t>
+          <t>61.00 x 33.80 x 32.30 cm</t>
         </is>
       </c>
       <c r="BR2" s="13" t="inlineStr">
         <is>
-          <t>标准包裹</t>
+          <t>轻型标准大件</t>
         </is>
       </c>
     </row>
@@ -1839,11 +1793,15 @@
       <c r="B3" s="13"/>
       <c r="C3" s="14" t="inlineStr">
         <is>
-          <t>B0G7GJZ7WQ</t>
+          <t>B0GL7P6391</t>
         </is>
       </c>
       <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
+      <c r="E3" s="14" t="inlineStr">
+        <is>
+          <t>Marque: JONR | Caractéristique spéciale: Duo-Clean | Type de filtre: Élément filtrant en éponge | Recommandation de surface: Tous étage confondu | Source d'alimentation: Alimenté par batterie | Tension: 20.0 | Composants inclus: Batterie | Sans fil ?: Non | Poids de l'article: 7,9 Livres | Capacité: 1500 milligrammes</t>
+        </is>
+      </c>
       <c r="F3" s="14" t="inlineStr">
         <is>
           <t>JONR</t>
@@ -1851,33 +1809,41 @@
       </c>
       <c r="G3" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/stores/JONR/page/2E11CD6D-6ABC-4227-8074-804128923C6D?lp_asin=B0H3NZP2VD&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.fr/stores/JONR/page/2E11CD6D-6ABC-4227-8074-804128923C6D?lp_asin=B0GL7P6391&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H3" s="14" t="inlineStr">
         <is>
-          <t>JONR Aspirateur Eau et poussière 20 000 Pa H2, Design innovant sans Odeur, réservoir d'eau Extra Large de 1500 ML avec Plat à</t>
-        </is>
-      </c>
-      <c r="I3" s="14"/>
+          <t>JONR Aspirateur sans fil avec eau chaude auto-nettoyante, design innovant de protection contre les odeurs, aspiration ouragan 20 000 Pa, 180 ° à plat sans perte de puissance et de capacité</t>
+        </is>
+      </c>
+      <c r="I3" s="14" t="inlineStr">
+        <is>
+          <t>JONR Aspirateur humide et sec H2 PRO (version améliorée du H2 – En s'appuyant sur les caractéristiques du H2, la fonction autonettoyante d'eau chaude à 70 °C et la fonction de séchage à l'air chaud ont été ajoutées. L'eau chaude autonettoyante à 70 °C élimine en profondeur les taches tenaces. Il utilise une méthode de séchage localisée unique, flexible, qui diffère de la rotation traditionnelle à grande vitesse. Notre méthode innovante prolonge considérablement la durée de vie du moteur et atteint un taux de séchage allant jusqu'à 90 %
+Design innovant sans odeur avec réservoir d'eau sale monté par le bas : l'aspirateur sec/humide JONR H2 Pro dispose d'un design innovant sans odeur avec un réservoir d'eau sale intégré au fond. Cela élimine définitivement les odeurs désagréables qui peuvent se développer avec les aspirateurs conventionnels après une utilisation prolongée. Le réservoir d'eau sale est facile à enlever et à rincer directement, assurant un fonctionnement durable sans odeur.
+Puissance d'aspiration de 20 000 Pa et positionnement à plat à 180° - L'aspirateur sec/humide JONR H2 PRO offre une aspiration puissante de 20 000 Pa, soit bien plus que l'aspirateur ED12 PRO MAX avec 17 000 Pa. Même à plat à 180°, la puissance d'aspiration et le volume utile du réservoir d'eau douce restent complètement inchangés. Contrairement aux appareils classiques où la puissance d'aspiration diminue et où le réservoir d'eau douce ne peut être utilisé qu'à mi-chemin, le H2 PRO résout parfaitement ce problème.
+Modl d'autonomie et de salle de bain de 45 minutes : l'aspirateur humide/sec JONR H2 PRO dispose d'un mode salle de bain exclusif qui améliore considérablement les performances de collecte et de séchage de l'eau pour les cuisines, les salles de bains, les piscines et autres zones humides – pour un nettoyage à sec unique et sans résidus. La batterie de 2600 mAh garantit une longue autonomie allant jusqu'à 45 minutes.
+Réservoir d'eau douce de 1500 ml et réservoir d'eau sale de 600 ml – Le JONR H2 Pro dispose d'un réservoir d'eau douce extra large de 1500 ml – deux fois la taille des appareils conventionnels (750 ml). Avec le réservoir d'eau sale de 600 ml, il permet une surface de nettoyage de plus de 300 m² par cycle de remplissage. Le remplissage fréquent est éliminé pour un nettoyage efficace et ininterrompu.</t>
+        </is>
+      </c>
       <c r="J3" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0G7GJZ7WQ?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0GL7P6391?psc=1</t>
         </is>
       </c>
       <c r="K3" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61ruaomVmXL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61beLprTKNL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L3" s="14" t="inlineStr">
         <is>
-          <t>B0G7GJZ7WQ</t>
+          <t>B0GWRWCTS1</t>
         </is>
       </c>
       <c r="M3" s="14" t="inlineStr">
         <is>
-          <t>Cuisine et Maison:Aspirateurs, entretien des sols et nettoyeurs de vitres:Aspirateurs:Aspirateurs balais et balais électriques</t>
+          <t>Cuisine et Maison:Aspirateurs, entretien des sols et nettoyeurs de vitres:Aspirateurs:Aspirateurs eau et poussière à usage domestique</t>
         </is>
       </c>
       <c r="N3" s="14" t="inlineStr">
@@ -1886,14 +1852,22 @@
         </is>
       </c>
       <c r="O3" s="15">
-        <v>1048114</v>
+        <v>1870511</v>
       </c>
       <c r="P3" s="2"/>
       <c r="Q3" s="16">
         <v>0</v>
       </c>
-      <c r="R3" s="17"/>
-      <c r="S3" s="18"/>
+      <c r="R3" s="17" t="inlineStr">
+        <is>
+          <t>Aspirateurs eau et poussière à usage domestique</t>
+        </is>
+      </c>
+      <c r="S3" s="18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="T3" s="15"/>
       <c r="U3" s="16"/>
       <c r="V3" s="15"/>
@@ -1902,93 +1876,65 @@
       <c r="Y3" s="19">
         <v>1</v>
       </c>
-      <c r="Z3" s="20">
-        <v>199.99</v>
-      </c>
+      <c r="Z3" s="20"/>
       <c r="AA3" s="4"/>
       <c r="AB3" s="1"/>
       <c r="AC3" s="2"/>
       <c r="AD3" s="19">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="AE3" s="15">
         <v>0</v>
       </c>
       <c r="AF3" s="21">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AG3" s="22">
         <v>0</v>
       </c>
       <c r="AH3" s="20">
-        <v>10.27</v>
+        <v>10.48</v>
       </c>
       <c r="AI3" s="16">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AJ3"/>
       <c r="AK3" s="13" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="AL3" s="19">
-        <v>173</v>
+        <v>138</v>
       </c>
       <c r="AM3" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AN3" s="13"/>
       <c r="AO3" s="13"/>
       <c r="AP3" s="4"/>
       <c r="AQ3" s="19">
-        <v>9</v>
-      </c>
-      <c r="AR3" s="19">
-        <v>1</v>
-      </c>
-      <c r="AS3" s="14" t="inlineStr">
-        <is>
-          <t>JONR Official</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="AR3" s="19"/>
+      <c r="AS3" s="14"/>
       <c r="AT3" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AU3" s="13" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="AV3" s="14" t="inlineStr">
-        <is>
-          <t>苏州市 江苏 215028 CN</t>
-        </is>
-      </c>
-      <c r="AW3" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1R6H4HF5LIC6Y</t>
-        </is>
-      </c>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AU3" s="13"/>
+      <c r="AV3" s="14"/>
+      <c r="AW3" s="13"/>
       <c r="AX3" s="13"/>
       <c r="AY3" s="13"/>
       <c r="AZ3" s="13"/>
       <c r="BA3" s="13"/>
       <c r="BB3" s="13"/>
-      <c r="BC3" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD3" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC3" s="13"/>
+      <c r="BD3" s="13"/>
       <c r="BE3" s="13"/>
       <c r="BF3" s="13"/>
       <c r="BG3" s="13"/>
@@ -1996,237 +1942,37 @@
       <c r="BI3"/>
       <c r="BJ3" s="23" t="inlineStr">
         <is>
-          <t>3.5 kg</t>
-        </is>
-      </c>
-      <c r="BK3" s="23" t="inlineStr">
-        <is>
-          <t>3.50 kg</t>
-        </is>
-      </c>
+          <t>7,9 Livres</t>
+        </is>
+      </c>
+      <c r="BK3" s="23"/>
       <c r="BL3" s="23" t="inlineStr">
         <is>
-          <t>26.9 x 21 x 109.9 cm</t>
-        </is>
-      </c>
-      <c r="BM3" s="23" t="inlineStr">
-        <is>
-          <t>26.90 x 21.00 x 109.90 cm</t>
-        </is>
-      </c>
+          <t>27L x 21l x 110H centimètres</t>
+        </is>
+      </c>
+      <c r="BM3" s="23"/>
       <c r="BN3" s="23" t="inlineStr">
         <is>
-          <t>6.78 kg</t>
+          <t>7.98 kg</t>
         </is>
       </c>
       <c r="BO3" s="23" t="inlineStr">
         <is>
-          <t>6.78 kg</t>
+          <t>7.98 kg</t>
         </is>
       </c>
       <c r="BP3" s="23" t="inlineStr">
         <is>
-          <t>61 x 33.8 x 32.3 cm</t>
+          <t>61.7 x 34.5 x 33 cm</t>
         </is>
       </c>
       <c r="BQ3" s="23" t="inlineStr">
         <is>
-          <t>61.00 x 33.80 x 32.30 cm</t>
+          <t>61.70 x 34.50 x 33.00 cm</t>
         </is>
       </c>
       <c r="BR3" s="13" t="inlineStr">
-        <is>
-          <t>轻型标准大件</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="13">
-        <v>3</v>
-      </c>
-      <c r="B4" s="13"/>
-      <c r="C4" s="14" t="inlineStr">
-        <is>
-          <t>B0GL7P6391</t>
-        </is>
-      </c>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14" t="inlineStr">
-        <is>
-          <t>Marque: JONR | Caractéristique spéciale: Duo-Clean | Type de filtre: Élément filtrant en éponge | Recommandation de surface: Tous étage confondu | Source d'alimentation: Alimenté par batterie | Tension: 20.0 | Composants inclus: Batterie | Sans fil ?: Non | Poids de l'article: 7,9 Livres | Capacité: 1500 milligrammes</t>
-        </is>
-      </c>
-      <c r="F4" s="14" t="inlineStr">
-        <is>
-          <t>JONR</t>
-        </is>
-      </c>
-      <c r="G4" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.fr/stores/JONR/page/2E11CD6D-6ABC-4227-8074-804128923C6D?lp_asin=B0GL7P6391&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
-        </is>
-      </c>
-      <c r="H4" s="14" t="inlineStr">
-        <is>
-          <t>JONR Aspirateur sans fil avec eau chaude auto-nettoyante, design innovant de protection contre les odeurs, aspiration ouragan 20 000 Pa, 180 ° à plat sans perte de puissance et de capacité</t>
-        </is>
-      </c>
-      <c r="I4" s="14" t="inlineStr">
-        <is>
-          <t>JONR Aspirateur humide et sec H2 PRO (version améliorée du H2 – En s'appuyant sur les caractéristiques du H2, la fonction autonettoyante d'eau chaude à 70 °C et la fonction de séchage à l'air chaud ont été ajoutées. L'eau chaude autonettoyante à 70 °C élimine en profondeur les taches tenaces. Il utilise une méthode de séchage localisée unique, flexible, qui diffère de la rotation traditionnelle à grande vitesse. Notre méthode innovante prolonge considérablement la durée de vie du moteur et atteint un taux de séchage allant jusqu'à 90 %
-Design innovant sans odeur avec réservoir d'eau sale monté par le bas : l'aspirateur sec/humide JONR H2 Pro dispose d'un design innovant sans odeur avec un réservoir d'eau sale intégré au fond. Cela élimine définitivement les odeurs désagréables qui peuvent se développer avec les aspirateurs conventionnels après une utilisation prolongée. Le réservoir d'eau sale est facile à enlever et à rincer directement, assurant un fonctionnement durable sans odeur.
-Puissance d'aspiration de 20 000 Pa et positionnement à plat à 180° - L'aspirateur sec/humide JONR H2 PRO offre une aspiration puissante de 20 000 Pa, soit bien plus que l'aspirateur ED12 PRO MAX avec 17 000 Pa. Même à plat à 180°, la puissance d'aspiration et le volume utile du réservoir d'eau douce restent complètement inchangés. Contrairement aux appareils classiques où la puissance d'aspiration diminue et où le réservoir d'eau douce ne peut être utilisé qu'à mi-chemin, le H2 PRO résout parfaitement ce problème.
-Modl d'autonomie et de salle de bain de 45 minutes : l'aspirateur humide/sec JONR H2 PRO dispose d'un mode salle de bain exclusif qui améliore considérablement les performances de collecte et de séchage de l'eau pour les cuisines, les salles de bains, les piscines et autres zones humides – pour un nettoyage à sec unique et sans résidus. La batterie de 2600 mAh garantit une longue autonomie allant jusqu'à 45 minutes.
-Réservoir d'eau douce de 1500 ml et réservoir d'eau sale de 600 ml – Le JONR H2 Pro dispose d'un réservoir d'eau douce extra large de 1500 ml – deux fois la taille des appareils conventionnels (750 ml). Avec le réservoir d'eau sale de 600 ml, il permet une surface de nettoyage de plus de 300 m² par cycle de remplissage. Le remplissage fréquent est éliminé pour un nettoyage efficace et ininterrompu.</t>
-        </is>
-      </c>
-      <c r="J4" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.fr/dp/B0GL7P6391?psc=1</t>
-        </is>
-      </c>
-      <c r="K4" s="14" t="inlineStr">
-        <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61beLprTKNL._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L4" s="14" t="inlineStr">
-        <is>
-          <t>B0GWRWCTS1</t>
-        </is>
-      </c>
-      <c r="M4" s="14" t="inlineStr">
-        <is>
-          <t>Cuisine et Maison:Aspirateurs, entretien des sols et nettoyeurs de vitres:Aspirateurs:Aspirateurs eau et poussière à usage domestique</t>
-        </is>
-      </c>
-      <c r="N4" s="14" t="inlineStr">
-        <is>
-          <t>Voir les 100 premiers en Cuisine et Maison</t>
-        </is>
-      </c>
-      <c r="O4" s="15">
-        <v>1870511</v>
-      </c>
-      <c r="P4" s="2"/>
-      <c r="Q4" s="16">
-        <v>0</v>
-      </c>
-      <c r="R4" s="17" t="inlineStr">
-        <is>
-          <t>Aspirateurs eau et poussière à usage domestique</t>
-        </is>
-      </c>
-      <c r="S4" s="18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T4" s="15"/>
-      <c r="U4" s="16"/>
-      <c r="V4" s="15"/>
-      <c r="W4" s="15"/>
-      <c r="X4" s="15"/>
-      <c r="Y4" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z4" s="20"/>
-      <c r="AA4" s="4"/>
-      <c r="AB4" s="1"/>
-      <c r="AC4" s="2"/>
-      <c r="AD4" s="19">
-        <v>36</v>
-      </c>
-      <c r="AE4" s="15">
-        <v>0</v>
-      </c>
-      <c r="AF4" s="21">
-        <v>3.4</v>
-      </c>
-      <c r="AG4" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH4" s="20">
-        <v>10.48</v>
-      </c>
-      <c r="AI4" s="16">
-        <v>0</v>
-      </c>
-      <c r="AJ4"/>
-      <c r="AK4" s="13" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="AL4" s="19">
-        <v>138</v>
-      </c>
-      <c r="AM4" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AN4" s="13"/>
-      <c r="AO4" s="13"/>
-      <c r="AP4" s="4"/>
-      <c r="AQ4" s="19">
-        <v>8</v>
-      </c>
-      <c r="AR4" s="19"/>
-      <c r="AS4" s="14"/>
-      <c r="AT4" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU4" s="13"/>
-      <c r="AV4" s="14"/>
-      <c r="AW4" s="13"/>
-      <c r="AX4" s="13"/>
-      <c r="AY4" s="13"/>
-      <c r="AZ4" s="13"/>
-      <c r="BA4" s="13"/>
-      <c r="BB4" s="13"/>
-      <c r="BC4" s="13"/>
-      <c r="BD4" s="13"/>
-      <c r="BE4" s="13"/>
-      <c r="BF4" s="13"/>
-      <c r="BG4" s="13"/>
-      <c r="BH4" s="14"/>
-      <c r="BI4"/>
-      <c r="BJ4" s="23" t="inlineStr">
-        <is>
-          <t>7,9 Livres</t>
-        </is>
-      </c>
-      <c r="BK4" s="23"/>
-      <c r="BL4" s="23" t="inlineStr">
-        <is>
-          <t>27L x 21l x 110H centimètres</t>
-        </is>
-      </c>
-      <c r="BM4" s="23"/>
-      <c r="BN4" s="23" t="inlineStr">
-        <is>
-          <t>7.98 kg</t>
-        </is>
-      </c>
-      <c r="BO4" s="23" t="inlineStr">
-        <is>
-          <t>7.98 kg</t>
-        </is>
-      </c>
-      <c r="BP4" s="23" t="inlineStr">
-        <is>
-          <t>61.7 x 34.5 x 33 cm</t>
-        </is>
-      </c>
-      <c r="BQ4" s="23" t="inlineStr">
-        <is>
-          <t>61.70 x 34.50 x 33.00 cm</t>
-        </is>
-      </c>
-      <c r="BR4" s="13" t="inlineStr">
         <is>
           <t>轻型标准大件</t>
         </is>
@@ -2236,35 +1982,98 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" tooltip="https://www.amazon.fr/dp/B0H69GTK93"/>
-    <hyperlink ref="G2" r:id="rId2" tooltip="https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Generic"/>
-    <hyperlink ref="J2" r:id="rId3" tooltip="https://www.amazon.fr/dp/B0H69GTK93?psc=1"/>
-    <hyperlink ref="K2" r:id="rId4" tooltip="https://images-na.ssl-images-amazon.com/images/I/710l9PXoMvL._AC_US600_.jpg"/>
-    <hyperlink ref="L2" r:id="rId5" tooltip="https://www.amazon.fr/dp/B0H69GTK93"/>
-    <hyperlink ref="M2" r:id="rId6" tooltip="https://www.amazon.fr/b?node=218877814031"/>
+    <hyperlink ref="C2" r:id="rId1" tooltip="https://www.amazon.fr/dp/B0G7GJZ7WQ"/>
+    <hyperlink ref="G2" r:id="rId2" tooltip="https://www.amazon.fr/stores/JONR/page/2E11CD6D-6ABC-4227-8074-804128923C6D?lp_asin=B0H3NZP2VD&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J2" r:id="rId3" tooltip="https://www.amazon.fr/dp/B0G7GJZ7WQ?psc=1"/>
+    <hyperlink ref="K2" r:id="rId4" tooltip="https://images-na.ssl-images-amazon.com/images/I/61ruaomVmXL._AC_US600_.jpg"/>
+    <hyperlink ref="L2" r:id="rId5" tooltip="https://www.amazon.fr/dp/B0G7GJZ7WQ"/>
+    <hyperlink ref="M2" r:id="rId6" tooltip="https://www.amazon.fr/b?node=3575230031"/>
     <hyperlink ref="N2" r:id="rId7"/>
-    <hyperlink ref="AW2" r:id="rId8" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AQBFEG6BI2O00"/>
-    <hyperlink ref="C3" r:id="rId9" tooltip="https://www.amazon.fr/dp/B0G7GJZ7WQ"/>
-    <hyperlink ref="G3" r:id="rId10" tooltip="https://www.amazon.fr/stores/JONR/page/2E11CD6D-6ABC-4227-8074-804128923C6D?lp_asin=B0H3NZP2VD&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J3" r:id="rId11" tooltip="https://www.amazon.fr/dp/B0G7GJZ7WQ?psc=1"/>
-    <hyperlink ref="K3" r:id="rId12" tooltip="https://images-na.ssl-images-amazon.com/images/I/61ruaomVmXL._AC_US600_.jpg"/>
-    <hyperlink ref="L3" r:id="rId13" tooltip="https://www.amazon.fr/dp/B0G7GJZ7WQ"/>
-    <hyperlink ref="M3" r:id="rId14" tooltip="https://www.amazon.fr/b?node=3575230031"/>
+    <hyperlink ref="AW2" r:id="rId8" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1R6H4HF5LIC6Y"/>
+    <hyperlink ref="C3" r:id="rId9" tooltip="https://www.amazon.fr/dp/B0GL7P6391"/>
+    <hyperlink ref="G3" r:id="rId10" tooltip="https://www.amazon.fr/stores/JONR/page/2E11CD6D-6ABC-4227-8074-804128923C6D?lp_asin=B0GL7P6391&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J3" r:id="rId11" tooltip="https://www.amazon.fr/dp/B0GL7P6391?psc=1"/>
+    <hyperlink ref="K3" r:id="rId12" tooltip="https://images-na.ssl-images-amazon.com/images/I/61beLprTKNL._AC_US600_.jpg"/>
+    <hyperlink ref="L3" r:id="rId13" tooltip="https://www.amazon.fr/dp/B0GWRWCTS1"/>
+    <hyperlink ref="M3" r:id="rId14" tooltip="https://www.amazon.fr/b?node=218877814031"/>
     <hyperlink ref="N3" r:id="rId15"/>
-    <hyperlink ref="AW3" r:id="rId16" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1R6H4HF5LIC6Y"/>
-    <hyperlink ref="C4" r:id="rId17" tooltip="https://www.amazon.fr/dp/B0GL7P6391"/>
-    <hyperlink ref="G4" r:id="rId18" tooltip="https://www.amazon.fr/stores/JONR/page/2E11CD6D-6ABC-4227-8074-804128923C6D?lp_asin=B0GL7P6391&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J4" r:id="rId19" tooltip="https://www.amazon.fr/dp/B0GL7P6391?psc=1"/>
-    <hyperlink ref="K4" r:id="rId20" tooltip="https://images-na.ssl-images-amazon.com/images/I/61beLprTKNL._AC_US600_.jpg"/>
-    <hyperlink ref="L4" r:id="rId21" tooltip="https://www.amazon.fr/dp/B0GWRWCTS1"/>
-    <hyperlink ref="M4" r:id="rId22" tooltip="https://www.amazon.fr/b?node=218877814031"/>
-    <hyperlink ref="N4" r:id="rId23"/>
   </hyperlinks>
-  <drawing r:id="rId24"/>
+  <drawing r:id="rId16"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="25" style="1" customWidth="1"/>
+    <col min="2" max="5" width="13" style="2" customWidth="1"/>
+    <col min="6" max="6" width="10" style="4" customWidth="1"/>
+    <col min="7" max="7" width="10" style="6" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>品牌</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>月销量</t>
+        </is>
+      </c>
+      <c r="C1" s="8" t="inlineStr">
+        <is>
+          <t>月销售额(€)</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>近1年销量</t>
+        </is>
+      </c>
+      <c r="E1" s="8" t="inlineStr">
+        <is>
+          <t>近一年销售额(€)</t>
+        </is>
+      </c>
+      <c r="F1" s="10" t="inlineStr">
+        <is>
+          <t>平均价格(€)</t>
+        </is>
+      </c>
+      <c r="G1" s="12" t="inlineStr">
+        <is>
+          <t>市场份额</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>JONR</t>
+        </is>
+      </c>
+      <c r="B2" s="15">
+        <v>0</v>
+      </c>
+      <c r="C2" s="15">
+        <v>0</v>
+      </c>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="22"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -2278,7 +2087,7 @@
     <row r="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>品牌</t>
+          <t>卖家</t>
         </is>
       </c>
       <c r="B1" s="8" t="inlineStr">
@@ -2315,28 +2124,24 @@
     <row r="2" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>Generic</t>
+          <t>JONR Official</t>
         </is>
       </c>
       <c r="B2" s="15">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C2" s="15">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="D2" s="15"/>
       <c r="E2" s="15"/>
-      <c r="F2" s="20">
-        <v>40.0</v>
-      </c>
-      <c r="G2" s="22">
-        <v>1.0</v>
-      </c>
+      <c r="F2" s="20"/>
+      <c r="G2" s="22"/>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="inlineStr">
         <is>
-          <t>JONR</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="B3" s="15">
@@ -2348,122 +2153,7 @@
       <c r="D3" s="15"/>
       <c r="E3" s="15"/>
       <c r="F3" s="20"/>
-      <c r="G3" s="22">
-        <v>0.0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="25" style="1" customWidth="1"/>
-    <col min="2" max="5" width="13" style="2" customWidth="1"/>
-    <col min="6" max="6" width="10" style="4" customWidth="1"/>
-    <col min="7" max="7" width="10" style="6" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="inlineStr">
-        <is>
-          <t>卖家</t>
-        </is>
-      </c>
-      <c r="B1" s="8" t="inlineStr">
-        <is>
-          <t>月销量</t>
-        </is>
-      </c>
-      <c r="C1" s="8" t="inlineStr">
-        <is>
-          <t>月销售额(€)</t>
-        </is>
-      </c>
-      <c r="D1" s="8" t="inlineStr">
-        <is>
-          <t>近1年销量</t>
-        </is>
-      </c>
-      <c r="E1" s="8" t="inlineStr">
-        <is>
-          <t>近一年销售额(€)</t>
-        </is>
-      </c>
-      <c r="F1" s="10" t="inlineStr">
-        <is>
-          <t>平均价格(€)</t>
-        </is>
-      </c>
-      <c r="G1" s="12" t="inlineStr">
-        <is>
-          <t>市场份额</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="14" t="inlineStr">
-        <is>
-          <t>CHENMW Department Store</t>
-        </is>
-      </c>
-      <c r="B2" s="15">
-        <v>6</v>
-      </c>
-      <c r="C2" s="15">
-        <v>240</v>
-      </c>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="20">
-        <v>40.0</v>
-      </c>
-      <c r="G2" s="22">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="inlineStr">
-        <is>
-          <t>JONR Official</t>
-        </is>
-      </c>
-      <c r="B3" s="15">
-        <v>0</v>
-      </c>
-      <c r="C3" s="15">
-        <v>0</v>
-      </c>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="22">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="14" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="B4" s="15">
-        <v>0</v>
-      </c>
-      <c r="C4" s="15">
-        <v>0</v>
-      </c>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="22">
-        <v>0.0</v>
-      </c>
+      <c r="G3" s="22"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
